--- a/docs/example_analysis/input_dataset/Example_dataset_Foreground_Background.xlsx
+++ b/docs/example_analysis/input_dataset/Example_dataset_Foreground_Background.xlsx
@@ -10151,7 +10151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4879F3B4-6D44-B943-9849-ED5D941EC7FF}">
-  <dimension ref="A1:A598"/>
+  <dimension ref="A1:A597"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -11759,1386 +11759,1381 @@
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>294</v>
+        <v>93</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>93</v>
+        <v>295</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
-        <v>296</v>
+        <v>130</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>130</v>
+        <v>297</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
-        <v>299</v>
+        <v>109</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
-        <v>109</v>
+        <v>300</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
-        <v>302</v>
+        <v>101</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
-        <v>96</v>
+        <v>303</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
-        <v>304</v>
+        <v>114</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
-        <v>142</v>
+        <v>305</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
-        <v>305</v>
+        <v>137</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
-        <v>137</v>
+        <v>306</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
-        <v>308</v>
+        <v>135</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
-        <v>310</v>
+        <v>122</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
-        <v>144</v>
+        <v>311</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
-        <v>315</v>
+        <v>157</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
-        <v>157</v>
+        <v>316</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
-        <v>316</v>
+        <v>132</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
-        <v>125</v>
+        <v>317</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
-        <v>319</v>
+        <v>134</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
-        <v>134</v>
+        <v>320</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
-        <v>320</v>
+        <v>127</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
-        <v>127</v>
+        <v>321</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
-        <v>322</v>
+        <v>228</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
-        <v>228</v>
+        <v>323</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
-        <v>332</v>
+        <v>54</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
-        <v>193</v>
+        <v>333</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
-        <v>334</v>
+        <v>124</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
-        <v>170</v>
+        <v>335</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
-        <v>335</v>
+        <v>188</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
-        <v>180</v>
+        <v>336</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
-        <v>337</v>
+        <v>218</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
-        <v>218</v>
+        <v>338</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
-        <v>338</v>
+        <v>254</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
-        <v>161</v>
+        <v>339</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
-        <v>342</v>
+        <v>151</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
-        <v>151</v>
+        <v>343</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
-        <v>343</v>
+        <v>27</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
-        <v>27</v>
+        <v>344</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
-        <v>344</v>
+        <v>173</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
-        <v>140</v>
+        <v>219</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
-        <v>219</v>
+        <v>145</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>145</v>
+        <v>345</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
-        <v>356</v>
+        <v>46</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
-        <v>46</v>
+        <v>357</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
-        <v>363</v>
+        <v>167</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
-        <v>167</v>
+        <v>364</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
-        <v>366</v>
+        <v>251</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
-        <v>251</v>
+        <v>367</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
-        <v>369</v>
+        <v>40</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
-        <v>40</v>
+        <v>370</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
-        <v>372</v>
+        <v>206</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
-        <v>206</v>
+        <v>373</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
-        <v>374</v>
+        <v>186</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
-        <v>186</v>
+        <v>375</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
-        <v>377</v>
+        <v>189</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
-        <v>189</v>
+        <v>378</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
-        <v>395</v>
+        <v>136</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
-        <v>136</v>
+        <v>396</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
-        <v>396</v>
+        <v>214</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
-        <v>214</v>
+        <v>397</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
-        <v>400</v>
+        <v>174</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
-        <v>174</v>
+        <v>401</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
-        <v>406</v>
+        <v>220</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
-        <v>178</v>
+        <v>407</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
-        <v>407</v>
+        <v>212</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
-        <v>212</v>
+        <v>408</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
-        <v>409</v>
+        <v>152</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
-        <v>152</v>
+        <v>410</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="s">
-        <v>417</v>
+        <v>223</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="s">
-        <v>223</v>
+        <v>418</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
-        <v>421</v>
+        <v>156</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="s">
-        <v>156</v>
+        <v>422</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="s">
-        <v>423</v>
+        <v>246</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="s">
-        <v>246</v>
+        <v>424</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="s">
-        <v>425</v>
+        <v>250</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="s">
-        <v>276</v>
+        <v>426</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A522" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A524" s="1" t="s">
-        <v>431</v>
+        <v>257</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A525" s="1" t="s">
-        <v>257</v>
+        <v>175</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A526" s="1" t="s">
-        <v>175</v>
+        <v>432</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A527" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A528" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="530" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="531" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="532" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="533" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="534" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="535" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="536" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="537" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="538" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="539" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="s">
-        <v>444</v>
+        <v>71</v>
       </c>
     </row>
     <row r="540" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A540" s="1" t="s">
-        <v>71</v>
+        <v>445</v>
       </c>
     </row>
     <row r="541" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A541" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="542" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A542" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="543" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A543" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="544" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A544" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="545" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A545" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="546" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A546" s="1" t="s">
-        <v>450</v>
+        <v>267</v>
       </c>
     </row>
     <row r="547" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A547" s="1" t="s">
-        <v>267</v>
+        <v>451</v>
       </c>
     </row>
     <row r="548" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A548" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="549" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A549" s="1" t="s">
-        <v>452</v>
+        <v>187</v>
       </c>
     </row>
     <row r="550" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A550" s="1" t="s">
-        <v>187</v>
+        <v>453</v>
       </c>
     </row>
     <row r="551" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A551" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="552" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A552" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="553" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A553" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="554" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A554" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="555" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A555" s="1" t="s">
-        <v>457</v>
+        <v>75</v>
       </c>
     </row>
     <row r="556" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A556" s="1" t="s">
-        <v>75</v>
+        <v>234</v>
       </c>
     </row>
     <row r="557" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A557" s="1" t="s">
-        <v>234</v>
+        <v>458</v>
       </c>
     </row>
     <row r="558" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A558" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="559" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A559" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="560" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A560" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="561" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A561" s="1" t="s">
-        <v>461</v>
+        <v>165</v>
       </c>
     </row>
     <row r="562" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A562" s="1" t="s">
-        <v>165</v>
+        <v>462</v>
       </c>
     </row>
     <row r="563" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A563" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="564" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A564" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="565" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A565" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="566" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A566" s="1" t="s">
-        <v>465</v>
+        <v>278</v>
       </c>
     </row>
     <row r="567" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A567" s="1" t="s">
-        <v>278</v>
+        <v>466</v>
       </c>
     </row>
     <row r="568" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A568" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="569" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A569" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="570" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A570" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="571" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A571" s="1" t="s">
-        <v>469</v>
+        <v>265</v>
       </c>
     </row>
     <row r="572" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A572" s="1" t="s">
-        <v>265</v>
+        <v>470</v>
       </c>
     </row>
     <row r="573" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A573" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="574" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A574" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="575" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A575" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="576" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A576" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="577" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A577" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="578" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A578" s="1" t="s">
-        <v>475</v>
+        <v>283</v>
       </c>
     </row>
     <row r="579" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A579" s="1" t="s">
-        <v>283</v>
+        <v>476</v>
       </c>
     </row>
     <row r="580" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A580" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="581" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A581" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="582" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A582" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="583" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A583" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="584" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A584" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="585" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A585" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="586" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A586" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="587" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A587" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="588" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A588" s="1" t="s">
-        <v>484</v>
+        <v>60</v>
       </c>
     </row>
     <row r="589" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A589" s="1" t="s">
-        <v>60</v>
+        <v>485</v>
       </c>
     </row>
     <row r="590" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A590" s="1" t="s">
-        <v>485</v>
+        <v>69</v>
       </c>
     </row>
     <row r="591" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A591" s="1" t="s">
-        <v>69</v>
+        <v>486</v>
       </c>
     </row>
     <row r="592" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A592" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="593" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A593" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="594" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A594" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="595" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A595" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="596" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A596" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="597" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A597" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="598" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A598" s="1" t="s">
         <v>83</v>
       </c>
     </row>
